--- a/260507/IncrementalStrain_PairResults.xlsx
+++ b/260507/IncrementalStrain_PairResults.xlsx
@@ -18,7 +18,7 @@
     <t>Label</t>
   </si>
   <si>
-    <t>1 → 4</t>
+    <t>No.1 → No.4</t>
   </si>
   <si>
     <t>Ef1_ID</t>
@@ -197,43 +197,43 @@
         <v>5</v>
       </c>
       <c r="D2" s="0">
-        <v>1.0020562560607247</v>
+        <v>1.0020276879125167</v>
       </c>
       <c r="E2" s="0">
-        <v>1.1030767971656876</v>
+        <v>1.1015942500866474</v>
       </c>
       <c r="F2" s="0">
-        <v>0.97109427769125001</v>
+        <v>0.9708162669194883</v>
       </c>
       <c r="G2" s="0">
-        <v>0.93545820541125246</v>
+        <v>0.93695839268181913</v>
       </c>
       <c r="H2" s="0">
-        <v>327.21881434592564</v>
+        <v>327.76589361892769</v>
       </c>
       <c r="I2" s="0">
-        <v>2.8777106942991399</v>
+        <v>2.3989997892703174</v>
       </c>
       <c r="J2" s="0">
-        <v>220.82310217540774</v>
+        <v>223.97814960466019</v>
       </c>
       <c r="K2" s="0">
-        <v>79.902377223065926</v>
+        <v>80.029922842955017</v>
       </c>
       <c r="L2" s="0">
-        <v>57.709611369566524</v>
+        <v>58.174973178737162</v>
       </c>
       <c r="M2" s="0">
-        <v>9.6706349465988968</v>
+        <v>9.6714193975572602</v>
       </c>
       <c r="N2" s="0">
-        <v>1.1359111288228601</v>
+        <v>1.1347093035246851</v>
       </c>
       <c r="O2" s="0">
-        <v>1.0380947775901233</v>
+        <v>1.0361359421102565</v>
       </c>
       <c r="P2" s="0">
-        <v>-0.54633423949519344</v>
+        <v>-0.56140990176087435</v>
       </c>
     </row>
   </sheetData>
